--- a/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_KeyInstall_20260917.xlsx
+++ b/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_KeyInstall_20260917.xlsx
@@ -4228,7 +4228,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4268,6 +4268,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4896,7 +4902,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="8" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="8" applyBorder="1"/>
@@ -5381,6 +5387,17 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="0" borderId="0" xfId="0"/>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Normal 2 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -9868,40 +9885,40 @@
       </c>
     </row>
     <row r="24" spans="1:34">
-      <c r="A24" s="87"/>
-      <c r="B24" s="81" t="str">
+      <c r="A24" s="180"/>
+      <c r="B24" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C24" s="82"/>
-      <c r="D24" s="81" t="inlineStr">
+      <c r="C24" s="178"/>
+      <c r="D24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-KeyInsyall-008</t>
         </is>
       </c>
-      <c r="E24" s="81"/>
-      <c r="F24" s="81" t="inlineStr">
+      <c r="E24" s="177"/>
+      <c r="F24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-KI-015</t>
         </is>
       </c>
-      <c r="G24" s="81" t="inlineStr">
+      <c r="G24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Key Install</t>
         </is>
       </c>
-      <c r="H24" s="81" t="inlineStr">
+      <c r="H24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Persistence</t>
         </is>
       </c>
-      <c r="I24" s="81" t="inlineStr">
+      <c r="I24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">The system shall guarantee that all imported client keys are encrypted using the KeyMint AIDL HAL and stored in a location immune to user-initiated erasures (e.g., Factory Reset).
 (key blob is still usable after an OTA or HAL version upgrade)</t>
         </is>
       </c>
-      <c r="J24" s="81" t="inlineStr">
+      <c r="J24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. A key blob is installed on the DUT
@@ -9909,95 +9926,95 @@
 4. The DUT has been power cycled</t>
         </is>
       </c>
-      <c r="K24" s="81" t="inlineStr">
+      <c r="K24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L24" s="81" t="inlineStr">
+      <c r="L24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;DUT-side trigger for OTA or HAL upgrade image provided by RD (X-j)&gt;
 $ &lt;command provided by RD (X-j)&gt;</t>
         </is>
       </c>
-      <c r="M24" s="81" t="inlineStr">
+      <c r="M24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;observable outcome provided by RD (X-j)&gt;</t>
         </is>
       </c>
-      <c r="N24" s="81" t="inlineStr">
+      <c r="N24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-008</t>
         </is>
       </c>
-      <c r="O24" s="81" t="inlineStr">
+      <c r="O24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P24" s="81" t="inlineStr">
+      <c r="P24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="Q24" s="81"/>
-      <c r="R24" s="81" t="inlineStr">
+      <c r="Q24" s="177"/>
+      <c r="R24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S24" s="81" t="inlineStr">
+      <c r="S24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T24" s="81" t="inlineStr">
+      <c r="T24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U24" s="81" t="inlineStr">
+      <c r="U24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V24" s="81" t="inlineStr">
+      <c r="V24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W24" s="81" t="inlineStr">
+      <c r="W24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X24" s="83" t="inlineStr">
+      <c r="X24" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y24" s="81" t="inlineStr">
+      <c r="Y24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z24" s="83" t="inlineStr">
+      <c r="Z24" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA24" s="83" t="inlineStr">
+      <c r="AA24" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB24" s="81"/>
-      <c r="AC24" s="81"/>
-      <c r="AD24" s="81"/>
-      <c r="AE24" s="81"/>
-      <c r="AF24" s="81"/>
-      <c r="AG24" s="81"/>
-      <c r="AH24" s="83" t="inlineStr">
+      <c r="AB24" s="177"/>
+      <c r="AC24" s="177"/>
+      <c r="AD24" s="177"/>
+      <c r="AE24" s="177"/>
+      <c r="AF24" s="177"/>
+      <c r="AG24" s="177"/>
+      <c r="AH24" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-KeyInsyall-008 Requirement Description and Verification Criteria
 sibling axis: persistence trigger; rule 5 of SEC-04 4.2
@@ -10292,133 +10309,133 @@
       </c>
     </row>
     <row r="27" spans="1:34">
-      <c r="A27" s="87"/>
-      <c r="B27" s="81" t="str">
+      <c r="A27" s="180"/>
+      <c r="B27" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C27" s="82"/>
-      <c r="D27" s="81" t="inlineStr">
+      <c r="C27" s="178"/>
+      <c r="D27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-KeyInsyall-010</t>
         </is>
       </c>
-      <c r="E27" s="81"/>
-      <c r="F27" s="81" t="inlineStr">
+      <c r="E27" s="177"/>
+      <c r="F27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-KI-018</t>
         </is>
       </c>
-      <c r="G27" s="81" t="inlineStr">
+      <c r="G27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Key Install</t>
         </is>
       </c>
-      <c r="H27" s="81" t="inlineStr">
+      <c r="H27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Crypto Service</t>
         </is>
       </c>
-      <c r="I27" s="81" t="inlineStr">
+      <c r="I27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">The KeyInstall feature shall restrict access to installed keys, allowing only a predefined list of authorized applications to perform cryptographic operations.
 (authorized application; access is granted and the operation completes)</t>
         </is>
       </c>
-      <c r="J27" s="81" t="inlineStr">
+      <c r="J27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)</t>
         </is>
       </c>
-      <c r="K27" s="81" t="inlineStr">
+      <c r="K27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L27" s="81" t="inlineStr">
+      <c r="L27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;KeyInstall status test runner provided by RD (X-f-2)&gt; is executed
 $ &lt;command provided by RD (X-f-2)&gt;</t>
         </is>
       </c>
-      <c r="M27" s="81" t="inlineStr">
+      <c r="M27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;KeyInstall status test runner provided by RD (X-f-2)&gt;</t>
         </is>
       </c>
-      <c r="N27" s="81" t="inlineStr">
+      <c r="N27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-010</t>
         </is>
       </c>
-      <c r="O27" s="81" t="inlineStr">
+      <c r="O27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P27" s="81" t="inlineStr">
+      <c r="P27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="Q27" s="81"/>
-      <c r="R27" s="81" t="inlineStr">
+      <c r="Q27" s="177"/>
+      <c r="R27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S27" s="81" t="inlineStr">
+      <c r="S27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T27" s="81" t="inlineStr">
+      <c r="T27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U27" s="81" t="inlineStr">
+      <c r="U27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V27" s="81" t="inlineStr">
+      <c r="V27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W27" s="81" t="inlineStr">
+      <c r="W27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X27" s="83" t="inlineStr">
+      <c r="X27" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y27" s="81" t="inlineStr">
+      <c r="Y27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z27" s="83" t="inlineStr">
+      <c r="Z27" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA27" s="83" t="inlineStr">
+      <c r="AA27" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB27" s="81"/>
-      <c r="AC27" s="81"/>
-      <c r="AD27" s="81"/>
-      <c r="AE27" s="81"/>
-      <c r="AF27" s="81"/>
-      <c r="AG27" s="81"/>
-      <c r="AH27" s="83" t="inlineStr">
+      <c r="AB27" s="177"/>
+      <c r="AC27" s="177"/>
+      <c r="AD27" s="177"/>
+      <c r="AE27" s="177"/>
+      <c r="AF27" s="177"/>
+      <c r="AG27" s="177"/>
+      <c r="AH27" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-KeyInsyall-010 Requirement Description and Verification Criteria
 sibling axis: client authorization; rule 1,3 of SEC-04 4.2
@@ -10430,50 +10447,50 @@
       </c>
     </row>
     <row r="28" spans="1:34">
-      <c r="A28" s="87"/>
-      <c r="B28" s="81" t="str">
+      <c r="A28" s="180"/>
+      <c r="B28" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C28" s="82"/>
-      <c r="D28" s="81" t="inlineStr">
+      <c r="C28" s="178"/>
+      <c r="D28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-KeyInsyall-010</t>
         </is>
       </c>
-      <c r="E28" s="81"/>
-      <c r="F28" s="81" t="inlineStr">
+      <c r="E28" s="177"/>
+      <c r="F28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-KI-019</t>
         </is>
       </c>
-      <c r="G28" s="81" t="inlineStr">
+      <c r="G28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Key Install</t>
         </is>
       </c>
-      <c r="H28" s="81" t="inlineStr">
+      <c r="H28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Crypto Service</t>
         </is>
       </c>
-      <c r="I28" s="81" t="inlineStr">
+      <c r="I28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">The KeyInstall feature shall restrict access to installed keys, allowing only a predefined list of authorized applications to perform cryptographic operations.
 (unauthorized application; the request is refused and a security violation is logged)</t>
         </is>
       </c>
-      <c r="J28" s="81" t="inlineStr">
+      <c r="J28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)</t>
         </is>
       </c>
-      <c r="K28" s="81" t="inlineStr">
+      <c r="K28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L28" s="81" t="inlineStr">
+      <c r="L28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;KeyInstall status test runner provided by RD (X-f-2)&gt; is executed
 $ &lt;command provided by RD (X-f-2)&gt;
@@ -10481,85 +10498,85 @@
 $ adb logcat -s KeyInstall</t>
         </is>
       </c>
-      <c r="M28" s="81" t="inlineStr">
+      <c r="M28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;KeyInstall status test runner provided by RD (X-f-2)&gt;
 2. &lt;log keyword provided by RD (X-h)&gt;</t>
         </is>
       </c>
-      <c r="N28" s="81" t="inlineStr">
+      <c r="N28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-010</t>
         </is>
       </c>
-      <c r="O28" s="81" t="inlineStr">
+      <c r="O28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P28" s="81" t="inlineStr">
+      <c r="P28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="Q28" s="81"/>
-      <c r="R28" s="81" t="inlineStr">
+      <c r="Q28" s="177"/>
+      <c r="R28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">負向測試 (Negative / Invalid)</t>
         </is>
       </c>
-      <c r="S28" s="81" t="inlineStr">
+      <c r="S28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T28" s="81" t="inlineStr">
+      <c r="T28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U28" s="81" t="inlineStr">
+      <c r="U28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V28" s="81" t="inlineStr">
+      <c r="V28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W28" s="81" t="inlineStr">
+      <c r="W28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X28" s="83" t="inlineStr">
+      <c r="X28" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y28" s="81" t="inlineStr">
+      <c r="Y28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z28" s="83" t="inlineStr">
+      <c r="Z28" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA28" s="83" t="inlineStr">
+      <c r="AA28" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB28" s="81"/>
-      <c r="AC28" s="81"/>
-      <c r="AD28" s="81"/>
-      <c r="AE28" s="81"/>
-      <c r="AF28" s="81"/>
-      <c r="AG28" s="81"/>
-      <c r="AH28" s="83" t="inlineStr">
+      <c r="AB28" s="177"/>
+      <c r="AC28" s="177"/>
+      <c r="AD28" s="177"/>
+      <c r="AE28" s="177"/>
+      <c r="AF28" s="177"/>
+      <c r="AG28" s="177"/>
+      <c r="AH28" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-KeyInsyall-010 Requirement Description and Verification Criteria
 sibling axis: client authorization; rule 1,3,4 of SEC-04 4.2
@@ -10854,51 +10871,51 @@
       </c>
     </row>
     <row r="31" spans="1:34">
-      <c r="A31" s="87"/>
-      <c r="B31" s="81" t="str">
+      <c r="A31" s="180"/>
+      <c r="B31" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C31" s="82"/>
-      <c r="D31" s="81" t="inlineStr">
+      <c r="C31" s="178"/>
+      <c r="D31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-KeyInsyall-012</t>
         </is>
       </c>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81" t="inlineStr">
+      <c r="E31" s="177"/>
+      <c r="F31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-KI-022</t>
         </is>
       </c>
-      <c r="G31" s="81" t="inlineStr">
+      <c r="G31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Key Install</t>
         </is>
       </c>
-      <c r="H31" s="81" t="inlineStr">
+      <c r="H31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Platform Compliance</t>
         </is>
       </c>
-      <c r="I31" s="81" t="inlineStr">
+      <c r="I31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">The KeyInstall feature shall adhere to Android 14 development and security standards, including:
 (no SELinux denial is recorded while KeyInstall runs in enforcing mode)</t>
         </is>
       </c>
-      <c r="J31" s="81" t="inlineStr">
+      <c r="J31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. The DUT runs in SELinux enforcing mode</t>
         </is>
       </c>
-      <c r="K31" s="81" t="inlineStr">
+      <c r="K31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L31" s="81" t="inlineStr">
+      <c r="L31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;DUT-side trigger for KeyInstall designated task execution provided by RD (X-f-2)&gt;
 $ &lt;command provided by RD (X-f-2)&gt;
@@ -10906,85 +10923,85 @@
 $ adb logcat -s avc</t>
         </is>
       </c>
-      <c r="M31" s="81" t="inlineStr">
+      <c r="M31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;observable outcome provided by RD (X-f-2)&gt;
 2. The adb logcat -s avc output contains no "avc: denied" entry related to KeyInstall</t>
         </is>
       </c>
-      <c r="N31" s="81" t="inlineStr">
+      <c r="N31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-012</t>
         </is>
       </c>
-      <c r="O31" s="81" t="inlineStr">
+      <c r="O31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P31" s="81" t="inlineStr">
+      <c r="P31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="Q31" s="81"/>
-      <c r="R31" s="81" t="inlineStr">
+      <c r="Q31" s="177"/>
+      <c r="R31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S31" s="81" t="inlineStr">
+      <c r="S31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T31" s="81" t="inlineStr">
+      <c r="T31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U31" s="81" t="inlineStr">
+      <c r="U31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V31" s="81" t="inlineStr">
+      <c r="V31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W31" s="81" t="inlineStr">
+      <c r="W31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X31" s="83" t="inlineStr">
+      <c r="X31" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y31" s="81" t="inlineStr">
+      <c r="Y31" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z31" s="83" t="inlineStr">
+      <c r="Z31" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA31" s="83" t="inlineStr">
+      <c r="AA31" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB31" s="81"/>
-      <c r="AC31" s="81"/>
-      <c r="AD31" s="81"/>
-      <c r="AE31" s="81"/>
-      <c r="AF31" s="81"/>
-      <c r="AG31" s="81"/>
-      <c r="AH31" s="83" t="inlineStr">
+      <c r="AB31" s="177"/>
+      <c r="AC31" s="177"/>
+      <c r="AD31" s="177"/>
+      <c r="AE31" s="177"/>
+      <c r="AF31" s="177"/>
+      <c r="AG31" s="177"/>
+      <c r="AH31" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-KeyInsyall-012 Requirement Description and Verification Criteria
 sibling axis: compliance check; rule 1 of SEC-04 4.2

--- a/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_KeyInstall_20260917.xlsx
+++ b/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_KeyInstall_20260917.xlsx
@@ -8004,7 +8004,19 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-001</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8146,7 +8158,19 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-001</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8288,7 +8312,19 @@
       </c>
       <c r="N12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-002</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O12" s="81" t="inlineStr">
@@ -8428,7 +8464,19 @@
       </c>
       <c r="N13" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-003</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O13" s="81" t="inlineStr">
@@ -8565,7 +8613,19 @@
       </c>
       <c r="N14" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-003</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O14" s="81" t="inlineStr">
@@ -8703,7 +8763,19 @@
       </c>
       <c r="N15" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-004</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O15" s="81" t="inlineStr">
@@ -8844,7 +8916,19 @@
       </c>
       <c r="N16" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-005</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O16" s="81" t="inlineStr">
@@ -8980,7 +9064,19 @@
       </c>
       <c r="N17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-006</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O17" s="81" t="inlineStr">
@@ -9116,7 +9212,19 @@
       </c>
       <c r="N18" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-006</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O18" s="81" t="inlineStr">
@@ -9252,7 +9360,19 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-006</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9388,7 +9508,19 @@
       </c>
       <c r="N20" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-006</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O20" s="81" t="inlineStr">
@@ -9529,7 +9661,23 @@
       </c>
       <c r="N21" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-007</t>
+          <t xml:space="preserve">CFTS084-134477
+CFTS084-134478
+CFTS084-134479
+CFTS084-134480
+CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O21" s="81" t="inlineStr">
@@ -9667,7 +9815,23 @@
       </c>
       <c r="N22" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-007</t>
+          <t xml:space="preserve">CFTS084-134477
+CFTS084-134478
+CFTS084-134479
+CFTS084-134480
+CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O22" s="81" t="inlineStr">
@@ -9806,7 +9970,20 @@
       </c>
       <c r="N23" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-008</t>
+          <t xml:space="preserve">CFTS084-134477
+CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O23" s="81" t="inlineStr">
@@ -9944,7 +10121,20 @@
       </c>
       <c r="N24" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-008</t>
+          <t xml:space="preserve">CFTS084-134477
+CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O24" s="177" t="inlineStr">
@@ -10084,7 +10274,19 @@
       </c>
       <c r="N25" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-009</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O25" s="81" t="inlineStr">
@@ -10226,7 +10428,19 @@
       </c>
       <c r="N26" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-009</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O26" s="81" t="inlineStr">
@@ -10365,7 +10579,19 @@
       </c>
       <c r="N27" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-010</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O27" s="177" t="inlineStr">
@@ -10506,7 +10732,19 @@
       </c>
       <c r="N28" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-010</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O28" s="177" t="inlineStr">
@@ -10648,7 +10886,19 @@
       </c>
       <c r="N29" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-011</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O29" s="81" t="inlineStr">
@@ -10789,7 +11039,19 @@
       </c>
       <c r="N30" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-011</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O30" s="81" t="inlineStr">
@@ -10931,7 +11193,19 @@
       </c>
       <c r="N31" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-012</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O31" s="177" t="inlineStr">
@@ -11069,7 +11343,19 @@
       </c>
       <c r="N32" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-012</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O32" s="81" t="inlineStr">
@@ -11207,7 +11493,19 @@
       </c>
       <c r="N33" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-012</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O33" s="81" t="inlineStr">
@@ -11347,7 +11645,19 @@
       </c>
       <c r="N34" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-KeyInstall-SWE1R1-V1.0_SWE1-KeyInsyall-013</t>
+          <t xml:space="preserve">CFTS084-134528
+CFTS084-134691
+CFTS084-134692
+CFTS084-134693
+CFTS084-134694
+CFTS084-134695
+CFTS084-134696
+CFTS084-134697
+CFTS084-134698
+CFTS084-134699
+CFTS084-134729
+CFTS084-134773
+CFTS084-134868</t>
         </is>
       </c>
       <c r="O34" s="81" t="inlineStr">

--- a/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_KeyInstall_20260917.xlsx
+++ b/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_KeyInstall_20260917.xlsx
@@ -8004,19 +8004,19 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8158,19 +8158,19 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8312,19 +8312,19 @@
       </c>
       <c r="N12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O12" s="81" t="inlineStr">
@@ -8464,19 +8464,19 @@
       </c>
       <c r="N13" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O13" s="81" t="inlineStr">
@@ -8613,19 +8613,19 @@
       </c>
       <c r="N14" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O14" s="81" t="inlineStr">
@@ -8763,19 +8763,19 @@
       </c>
       <c r="N15" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O15" s="81" t="inlineStr">
@@ -8916,19 +8916,19 @@
       </c>
       <c r="N16" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O16" s="81" t="inlineStr">
@@ -9064,19 +9064,19 @@
       </c>
       <c r="N17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O17" s="81" t="inlineStr">
@@ -9212,19 +9212,19 @@
       </c>
       <c r="N18" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O18" s="81" t="inlineStr">
@@ -9360,19 +9360,19 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9508,19 +9508,19 @@
       </c>
       <c r="N20" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O20" s="81" t="inlineStr">
@@ -9661,23 +9661,23 @@
       </c>
       <c r="N21" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134477
-CFTS084-134478
-CFTS084-134479
-CFTS084-134480
-CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949457
+CFTS084-4949458
+CFTS084-4949459
+CFTS084-4949461
+CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O21" s="81" t="inlineStr">
@@ -9815,23 +9815,23 @@
       </c>
       <c r="N22" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134477
-CFTS084-134478
-CFTS084-134479
-CFTS084-134480
-CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949457
+CFTS084-4949458
+CFTS084-4949459
+CFTS084-4949461
+CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O22" s="81" t="inlineStr">
@@ -9970,20 +9970,20 @@
       </c>
       <c r="N23" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134477
-CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949457
+CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O23" s="81" t="inlineStr">
@@ -10121,20 +10121,20 @@
       </c>
       <c r="N24" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134477
-CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949457
+CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O24" s="177" t="inlineStr">
@@ -10274,19 +10274,19 @@
       </c>
       <c r="N25" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O25" s="81" t="inlineStr">
@@ -10428,19 +10428,19 @@
       </c>
       <c r="N26" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O26" s="81" t="inlineStr">
@@ -10579,19 +10579,19 @@
       </c>
       <c r="N27" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O27" s="177" t="inlineStr">
@@ -10732,19 +10732,19 @@
       </c>
       <c r="N28" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O28" s="177" t="inlineStr">
@@ -10886,19 +10886,19 @@
       </c>
       <c r="N29" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O29" s="81" t="inlineStr">
@@ -11039,19 +11039,19 @@
       </c>
       <c r="N30" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O30" s="81" t="inlineStr">
@@ -11193,19 +11193,19 @@
       </c>
       <c r="N31" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O31" s="177" t="inlineStr">
@@ -11343,19 +11343,19 @@
       </c>
       <c r="N32" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O32" s="81" t="inlineStr">
@@ -11493,19 +11493,19 @@
       </c>
       <c r="N33" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O33" s="81" t="inlineStr">
@@ -11645,19 +11645,19 @@
       </c>
       <c r="N34" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134528
-CFTS084-134691
-CFTS084-134692
-CFTS084-134693
-CFTS084-134694
-CFTS084-134695
-CFTS084-134696
-CFTS084-134697
-CFTS084-134698
-CFTS084-134699
-CFTS084-134729
-CFTS084-134773
-CFTS084-134868</t>
+          <t xml:space="preserve">CFTS084-4949528
+CFTS084-4949736
+CFTS084-4949737
+CFTS084-4949738
+CFTS084-4949739
+CFTS084-4949740
+CFTS084-4949741
+CFTS084-4949742
+CFTS084-4949743
+CFTS084-4949744
+CFTS084-4949776
+CFTS084-4949821
+CFTS084-4949931</t>
         </is>
       </c>
       <c r="O34" s="81" t="inlineStr">
